--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,41 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hoover, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Java Enterprise Architect in Irvine, CA</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Sr Java Enterprise Architect in Irvine, CA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>True Religion Brand Jeans</t>
+          <t>ValueBase Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,75 +601,145 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>True Religion Brand Jeans</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Cloud Solutions Architect</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Regions Financial</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Hoover, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>11.1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
         </is>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Egypt</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, ECS</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89355d34c2e7d21</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Egypt</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt, AR, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb073c25dabf3264</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Sr Java Enterprise Architect in Irvine, CA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>ValueBase Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Java Enterprise Architect in Irvine, CA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
         </is>
       </c>
     </row>
@@ -742,6 +742,41 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Packaged/SaaS Application Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>IT Database Administrator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Java Enterprise Architect in Irvine, CA</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Hive, Spark, Scala, MySQL, MongoDB, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,147 +636,567 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fb936710c23398</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>True Religion Brand Jeans</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect</t>
+          <t>Sr Java Enterprise Architect in Irvine, CA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>ValueBase Consulting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bessemer Trust</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Woodbridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer IV</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Availity, LLC.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>True Religion Brand Jeans</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Copart, Inc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AWS Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arkatechture</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hoover, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Core BTS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Northwestern Medicine</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Packaged/SaaS Application Engineer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Accenture</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D19" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer I Application Development- Mid Tier</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9ee38245dd8f15c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Hadoop Big Data Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1ee56096500177</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Database Administrator</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
+          <t>https://www.indeed.com/viewjob?jk=c844b36a2e1bda08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Database Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS DevOps Datadog</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Spark, Scala, MySQL, MongoDB, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fb936710c23398</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff539c3ae99f7727</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,89 +706,89 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Java Enterprise Architect in Irvine, CA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c0763ad74d36902</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>True Religion Brand Jeans</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Hive, Spark, Scala, MySQL, MongoDB, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fb936710c23398</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=961c1329ccf392e7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III Full-Stack Development</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II Full-Stack Development</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,40 +1161,1055 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f1f7ac1d6409a8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bf583c77e4c9d72</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>True Religion Brand Jeans</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Vericast</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Western Union</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Copart, Inc</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0ffc09421c310dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82fe4e268dbb7b66</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8edb1a5d7881fc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AWS Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arkatechture</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Salesforce Development Engineer III</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hoover, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Core BTS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42cffb5d56f9eeaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Northwestern Medicine</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cloud Architect (Azure)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>The Akanksha LLC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Packaged/SaaS Application Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Software Engineer I Application Development- Mid Tier</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D51" t="n">
         <v>10.4</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ee38245dd8f15c</t>
         </is>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Big Data Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1ee56096500177</t>
+          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>IT Database Administrator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c844b36a2e1bda08</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AWS DevOps Datadog</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Database Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS DevOps Datadog</t>
+          <t>BI Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Boston Beer Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff539c3ae99f7727</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c0763ad74d36902</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c1329ccf392e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Cloud Developer 3 – Contract Position</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>True Religion Brand Jeans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f1f7ac1d6409a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,104 +1186,104 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf583c77e4c9d72</t>
+          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>True Religion Brand Jeans</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ffc09421c310dd</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe4e268dbb7b66</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe4e268dbb7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=8edb1a5d7881fc44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edb1a5d7881fc44</t>
+          <t>https://www.indeed.com/viewjob?jk=77098ecf48edec11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cffb5d56f9eeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Architect (Azure)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Northwestern Medicine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Cloud Architect (Azure)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III Full-Stack Development</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II Full-Stack Development</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer I Application Development- Mid Tier</t>
+          <t>Packaged/SaaS Application Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,15 +2201,225 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer III Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer I Application Development- Mid Tier</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ee38245dd8f15c</t>
         </is>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Database Administrator</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS DevOps Datadog</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
+          <t>https://www.indeed.com/viewjob?jk=c4430f4f7148ec3b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BI Data Engineer II</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Boston Beer Company</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Database Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS DevOps Datadog</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>BI Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>The Boston Beer Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hive, Spark, Scala, MySQL, MongoDB, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fb936710c23398</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Developer 3 – Contract Position</t>
+          <t>Senior Security Automation &amp; SOAR Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
+          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Cloud Developer</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>True Religion Brand Jeans</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Cloud Developer 3 – Contract Position</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Azure Cloud Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,137 +1406,137 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Innovative Tech Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fe4e268dbb7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>True Religion Brand Jeans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edb1a5d7881fc44</t>
+          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI Developer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77098ecf48edec11</t>
+          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
+          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect</t>
+          <t>Software Engineer III - AI Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+          <t>https://www.indeed.com/viewjob?jk=77098ecf48edec11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Architect (Azure)</t>
+          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk, pytest, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=398c49826e4fa255</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III Full-Stack Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II Full-Stack Development</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer I Application Development- Mid Tier</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Northwestern Medicine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,15 +2411,575 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Azure Integration Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>intent design ltd</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Azure Integration Architect</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Intent Design Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Quality Assurance (QA) Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Beck's Hybrids</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Atlanta, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42f536ef71f672fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cloud Architect (Azure)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>The Akanksha LLC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Packaged/SaaS Application Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer III Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Engineer I Application Development- Mid Tier</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ee38245dd8f15c</t>
         </is>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect (Cloud Transformation)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7e6b8f9c661779</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4430f4f7148ec3b</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=c4430f4f7148ec3b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT Database Administrator</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS DevOps Datadog</t>
+          <t>IT Database Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4bd2e62694461e</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Security Automation &amp; SOAR Engineer</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Senior Security Automation &amp; SOAR Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Developer 3 – Contract Position</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Cloud Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Cloud Developer 3 – Contract Position</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Azure Cloud Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Innovative Tech Solutions</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>True Religion Brand Jeans</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Innovative Tech Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI Developer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77098ecf48edec11</t>
+          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>intent design ltd</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance (QA) Engineer</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Beck's Hybrids</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f536ef71f672fc</t>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Architect (Azure)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Northwestern Medicine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Senior Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Beck's Hybrids</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=42f536ef71f672fc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>intent design ltd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Intent Design Pvt Ltd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III Full-Stack Development</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II Full-Stack Development</t>
+          <t>Cloud Architect (Azure)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer I Application Development- Mid Tier</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,330 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>The Akanksha LLC</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Packaged/SaaS Application Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer III Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer I Application Development- Mid Tier</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ee38245dd8f15c</t>
         </is>

--- a/results/job_matches_2026-07-27.xlsx
+++ b/results/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4430f4f7148ec3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Enterprise Information Architect I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>L.L. Bean, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Freeport, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=fea98a47c7da3e79</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Security Automation &amp; SOAR Engineer</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,49 +1231,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Security Automation &amp; SOAR Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Developer 3 – Contract Position</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Cloud Developer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Cloud Developer 3 – Contract Position</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Azure Cloud Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Innovative Tech Solutions</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f5eebdb7f2a13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
+          <t>https://www.indeed.com/viewjob?jk=74752f7f2514626c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Innovative Tech Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
         </is>
       </c>
     </row>
@@ -2153,20 +2153,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk, pytest, Git, CloudWatch</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398c49826e4fa255</t>
+          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk, pytest, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=398c49826e4fa255</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e8d45fd09212b1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance (QA) Engineer</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Beck's Hybrids</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, IN, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f536ef71f672fc</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>intent design ltd</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Architect (Azure)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Northwestern Medicine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Beck's Hybrids</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Atlanta, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=42f536ef71f672fc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>intent design ltd</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Intent Design Pvt Ltd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III Full-Stack Development</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II Full-Stack Development</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer I Application Development- Mid Tier</t>
+          <t>Cloud Architect (Azure)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,365 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>The Akanksha LLC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Packaged/SaaS Application Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer III Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fae7357d59e588</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full-Stack Development</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a1075545e0fb107</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer I Application Development- Mid Tier</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>S3, RDS, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ee38245dd8f15c</t>
         </is>
